--- a/Era_时代表.xlsx
+++ b/Era_时代表.xlsx
@@ -263,7 +263,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" s="0" t="b">
         <v>1</v>
